--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1892-newl.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1892-newl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17ACC217-B9A1-4C5E-B432-73B932562136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0EACF7C-9C7B-4AD7-B9AB-E243C8CEFDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1057,7 +1057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1277,10 +1277,6 @@
     <xf numFmtId="3" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1293,7 +1289,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1535,23 +1533,23 @@
         <v>280</v>
       </c>
       <c r="M1" s="68"/>
-      <c r="N1" s="87" t="s">
+      <c r="N1" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="87"/>
-      <c r="U1" s="87"/>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
+      <c r="R1" s="93"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="93"/>
+      <c r="U1" s="93"/>
+      <c r="V1" s="93"/>
+      <c r="W1" s="93"/>
+      <c r="X1" s="93"/>
+      <c r="Y1" s="93"/>
+      <c r="Z1" s="93"/>
+      <c r="AA1" s="93"/>
+      <c r="AB1" s="93"/>
       <c r="AD1" s="72" t="s">
         <v>281</v>
       </c>
@@ -1975,77 +1973,75 @@
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
     </row>
-    <row r="8" spans="1:42" s="88" customFormat="1">
-      <c r="A8" s="89" t="s">
+    <row r="8" spans="1:42" s="4" customFormat="1">
+      <c r="A8" s="87" t="s">
         <v>294</v>
       </c>
-      <c r="B8" s="94">
+      <c r="B8" s="92">
         <f>SUM(N8:O8)</f>
         <v>392136</v>
       </c>
-      <c r="C8" s="94">
+      <c r="C8" s="92">
         <f>SUM(N9:O9)</f>
         <v>2805</v>
       </c>
-      <c r="D8" s="94">
+      <c r="D8" s="92">
         <f>SUM(N10:O10)</f>
         <v>3236</v>
       </c>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="4"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="89"/>
       <c r="N8" s="15">
         <v>134206</v>
       </c>
       <c r="O8" s="15">
         <v>257930</v>
       </c>
-      <c r="P8" s="92"/>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="92"/>
-      <c r="S8" s="93"/>
-      <c r="T8" s="92"/>
-      <c r="U8" s="90"/>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="90"/>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-      <c r="AD8" s="95"/>
-      <c r="AE8" s="95"/>
-      <c r="AF8" s="95"/>
-      <c r="AH8" s="95"/>
-      <c r="AI8" s="95"/>
-      <c r="AJ8" s="95"/>
-      <c r="AL8" s="95"/>
-      <c r="AM8" s="95"/>
-      <c r="AO8" s="95"/>
-      <c r="AP8" s="95"/>
-    </row>
-    <row r="9" spans="1:42" s="88" customFormat="1">
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="91"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="88"/>
+      <c r="Y8" s="88"/>
+      <c r="Z8" s="88"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="88"/>
+      <c r="AD8" s="92">
+        <f>B8</f>
+        <v>392136</v>
+      </c>
+      <c r="AE8" s="92">
+        <f>C8</f>
+        <v>2805</v>
+      </c>
+      <c r="AF8" s="92">
+        <f>D8</f>
+        <v>3236</v>
+      </c>
+      <c r="AH8" s="88"/>
+      <c r="AI8" s="88"/>
+      <c r="AJ8" s="88"/>
+      <c r="AL8" s="88"/>
+      <c r="AM8" s="88"/>
+      <c r="AO8" s="88"/>
+      <c r="AP8" s="88"/>
+    </row>
+    <row r="9" spans="1:42" s="4" customFormat="1">
       <c r="A9" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
       <c r="K9" s="49"/>
       <c r="L9" s="49"/>
-      <c r="M9" s="4"/>
       <c r="N9" s="10" t="s">
         <v>14</v>
       </c>
@@ -2057,31 +2053,13 @@
       <c r="R9" s="5"/>
       <c r="S9" s="10"/>
       <c r="T9" s="5"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
-    </row>
-    <row r="10" spans="1:42" s="88" customFormat="1">
+    </row>
+    <row r="10" spans="1:42" s="4" customFormat="1">
       <c r="A10" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
       <c r="K10" s="49"/>
       <c r="L10" s="49"/>
-      <c r="M10" s="4"/>
       <c r="N10" s="10" t="s">
         <v>14</v>
       </c>
@@ -2093,14 +2071,6 @@
       <c r="R10" s="5"/>
       <c r="S10" s="10"/>
       <c r="T10" s="5"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
     </row>
     <row r="11" spans="1:42" customFormat="1">
       <c r="A11" s="14" t="s">
@@ -4299,27 +4269,27 @@
       <c r="AB41" s="23"/>
       <c r="AD41" s="83">
         <f>SUM(AD2:AD38)</f>
-        <v>19966951</v>
+        <v>20359087</v>
       </c>
       <c r="AE41" s="83">
         <f>SUM(AE2:AE38)</f>
-        <v>897800</v>
+        <v>900605</v>
       </c>
       <c r="AF41" s="83">
         <f>SUM(AF2:AF38)</f>
-        <v>678989</v>
+        <v>682225</v>
       </c>
       <c r="AH41" s="83">
         <f>B41-AD41</f>
-        <v>395324</v>
+        <v>3188</v>
       </c>
       <c r="AI41" s="83">
         <f>C41-AE41</f>
-        <v>2187</v>
+        <v>-618</v>
       </c>
       <c r="AJ41" s="83">
         <f>D41-AF41</f>
-        <v>3170</v>
+        <v>-66</v>
       </c>
       <c r="AL41" s="82">
         <f>C41/B41*1000</f>
@@ -15394,27 +15364,27 @@
       <c r="AB194" s="26"/>
       <c r="AD194" s="84">
         <f>SUM(AD41, AD73, AD83, AD190, AD191)</f>
-        <v>99444639</v>
+        <v>99836775</v>
       </c>
       <c r="AE194" s="84">
         <f>SUM(AE41, AE73, AE83, AE190, AE191)</f>
-        <v>4359935</v>
+        <v>4362740</v>
       </c>
       <c r="AF194" s="84">
         <f>SUM(AF41, AF73, AF83, AF190, AF191)</f>
-        <v>3822545</v>
+        <v>3825781</v>
       </c>
       <c r="AH194" s="83">
         <f>B194-AD194</f>
-        <v>806871</v>
+        <v>414735</v>
       </c>
       <c r="AI194" s="83">
         <f>C194-AE194</f>
-        <v>475577</v>
+        <v>472772</v>
       </c>
       <c r="AJ194" s="83">
         <f>D194-AF194</f>
-        <v>100276</v>
+        <v>97040</v>
       </c>
       <c r="AL194" s="82">
         <f>C194/B194*1000</f>
@@ -20543,27 +20513,27 @@
       <c r="AB274" s="47"/>
       <c r="AD274" s="84">
         <f>SUM(AD194, AD223, AD249, AD273)</f>
-        <v>118375751</v>
+        <v>118767887</v>
       </c>
       <c r="AE274" s="84">
         <f>SUM(AE194, AE223, AE249, AE273)</f>
-        <v>4970017</v>
+        <v>4972822</v>
       </c>
       <c r="AF274" s="84">
         <f>SUM(AF194, AF223, AF249, AF273)</f>
-        <v>4401235</v>
+        <v>4404471</v>
       </c>
       <c r="AH274" s="83">
         <f t="shared" si="6"/>
-        <v>913053</v>
+        <v>520917</v>
       </c>
       <c r="AI274" s="83">
         <f t="shared" si="6"/>
-        <v>6369</v>
+        <v>3564</v>
       </c>
       <c r="AJ274" s="83">
         <f t="shared" si="6"/>
-        <v>2666</v>
+        <v>-570</v>
       </c>
       <c r="AK274"/>
       <c r="AL274" s="82">

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1892-newl.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1892-newl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0EACF7C-9C7B-4AD7-B9AB-E243C8CEFDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78329BF5-71E4-4C51-8F93-A6B5EDD1758B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1792,10 +1792,12 @@
         <v>531805</v>
       </c>
       <c r="C5" s="15">
-        <v>31603</v>
+        <f>31603-C8</f>
+        <v>28798</v>
       </c>
       <c r="D5" s="15">
-        <v>44844</v>
+        <f>44844-D8</f>
+        <v>41608</v>
       </c>
       <c r="E5" s="16">
         <v>119717</v>
@@ -1865,28 +1867,28 @@
       </c>
       <c r="AI5" s="73">
         <f>AE5-C5</f>
-        <v>-2805</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="73">
         <f>AF5-D5</f>
-        <v>-3236</v>
+        <v>0</v>
       </c>
       <c r="AL5" s="74">
         <f>C5/B5*1000</f>
-        <v>59.425917394533712</v>
+        <v>54.151427684959714</v>
       </c>
       <c r="AM5" s="74">
         <f>D5/B5*1000</f>
-        <v>84.324141367606543</v>
+        <v>78.23920421959177</v>
       </c>
       <c r="AN5" s="79"/>
       <c r="AO5" s="74">
         <f>AL5-K5</f>
-        <v>5.2259173945337096</v>
+        <v>-4.8572315040289027E-2</v>
       </c>
       <c r="AP5" s="74">
         <f>AM5-L5</f>
-        <v>5.9241413676065378</v>
+        <v>-0.16079578040823606</v>
       </c>
     </row>
     <row r="6" spans="1:42" customFormat="1">
